--- a/artfynd/A 48284-2023 artfynd.xlsx
+++ b/artfynd/A 48284-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>115320239</v>
       </c>
       <c r="B2" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57740</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,14 +714,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Trunhatten SV, Skogskärr, Nrk</t>
+          <t>trunhatten v, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466858</v>
+        <v>466863</v>
       </c>
       <c r="R2" t="n">
-        <v>6546781</v>
+        <v>6546727</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -773,7 +768,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Träder utmärkt med en guldballong Hackringar på tall</t>
+          <t>Trädet utmärkt med en guldballong Hackringar på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,6 +792,692 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130099895</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Trunhatten SV, Skogskärr, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>466873</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6546721</v>
+      </c>
+      <c r="S3" t="n">
+        <v>20</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack med savflöde på tall på redan känt fynd. Rikligt med ringhack, äldre längre ner, färska längre upp. Märkt med rött märkband.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130100117</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Trunhatten SV, Skogskärr, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>466982</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6546751</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre födohack på rötad stubbe</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130100311</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97686</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Trunhatten SV, Trunhatten SV, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>466885</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6546699</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130100329</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Trunhatten SV, Skogskärr, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>466870</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6546669</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska födohack vid basen av stående död tall</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130100671</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Trunhatten SV, Skogskärr, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>466850</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6546462</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre födohack på stående död tall</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130100678</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Trunhatten SV, Skogskärr, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>466844</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6546459</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48284-2023 artfynd.xlsx
+++ b/artfynd/A 48284-2023 artfynd.xlsx
@@ -1032,7 +1032,7 @@
         <v>130100311</v>
       </c>
       <c r="B5" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 48284-2023 artfynd.xlsx
+++ b/artfynd/A 48284-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>115320239</v>
       </c>
       <c r="B2" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>130099895</v>
       </c>
       <c r="B3" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>130100117</v>
       </c>
       <c r="B4" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>130100311</v>
       </c>
       <c r="B5" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>130100329</v>
       </c>
       <c r="B6" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>130100671</v>
       </c>
       <c r="B7" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>130100678</v>
       </c>
       <c r="B8" t="n">
-        <v>58113</v>
+        <v>58198</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 48284-2023 artfynd.xlsx
+++ b/artfynd/A 48284-2023 artfynd.xlsx
@@ -1032,7 +1032,7 @@
         <v>130100311</v>
       </c>
       <c r="B5" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 48284-2023 artfynd.xlsx
+++ b/artfynd/A 48284-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115320239</v>
+        <v>130100117</v>
       </c>
       <c r="B2" t="n">
-        <v>57826</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -704,27 +704,24 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>trunhatten v, Skogskärr, Nrk</t>
+          <t>Trunhatten SV, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466863</v>
+        <v>466982</v>
       </c>
       <c r="R2" t="n">
-        <v>6546727</v>
+        <v>6546751</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,27 +745,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Trädet utmärkt med en guldballong Hackringar på tall</t>
+          <t>Äldre födohack på rötad stubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,27 +792,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130099895</v>
+        <v>130100329</v>
       </c>
       <c r="B3" t="n">
-        <v>57826</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -835,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466873</v>
+        <v>466870</v>
       </c>
       <c r="R3" t="n">
-        <v>6546721</v>
+        <v>6546669</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -870,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Färska ringhack med savflöde på tall på redan känt fynd. Rikligt med ringhack, äldre längre ner, färska längre upp. Märkt med rött märkband.</t>
+          <t>Färska födohack vid basen av stående död tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,14 +909,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130100117</v>
+        <v>130100656</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -952,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466982</v>
+        <v>466855</v>
       </c>
       <c r="R4" t="n">
-        <v>6546751</v>
+        <v>6546475</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -987,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre födohack på rötad stubbe</t>
+          <t>Äldre födohack vid basen av död tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130100311</v>
+        <v>130100671</v>
       </c>
       <c r="B5" t="n">
-        <v>97794</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,34 +1037,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Trunhatten SV, Trunhatten SV, Nrk</t>
+          <t>Trunhatten SV, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466885</v>
+        <v>466850</v>
       </c>
       <c r="R5" t="n">
-        <v>6546699</v>
+        <v>6546462</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1099,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre födohack på stående död tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,14 +1143,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130100329</v>
+        <v>130101147</v>
       </c>
       <c r="B6" t="n">
-        <v>57823</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1167,7 +1174,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1176,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466870</v>
+        <v>466684</v>
       </c>
       <c r="R6" t="n">
-        <v>6546669</v>
+        <v>6546698</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1211,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,12 +1228,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska födohack vid basen av stående död tall</t>
+          <t>Äldre födohack på grov granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130100671</v>
+        <v>115320239</v>
       </c>
       <c r="B7" t="n">
-        <v>57823</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1264,16 +1271,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1282,24 +1289,27 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Trunhatten SV, Skogskärr, Nrk</t>
+          <t>trunhatten v, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466850</v>
+        <v>466863</v>
       </c>
       <c r="R7" t="n">
-        <v>6546462</v>
+        <v>6546727</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,27 +1333,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Äldre födohack på stående död tall</t>
+          <t>Trädet utmärkt med en guldballong Hackringar på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,27 +1380,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130100678</v>
+        <v>130099895</v>
       </c>
       <c r="B8" t="n">
-        <v>58198</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1398,9 +1408,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1409,10 +1420,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466844</v>
+        <v>466873</v>
       </c>
       <c r="R8" t="n">
-        <v>6546459</v>
+        <v>6546721</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1444,7 +1455,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1454,7 +1465,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack med savflöde på tall på redan känt fynd. Rikligt med ringhack, äldre längre ner, färska längre upp. Märkt med rött märkband.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,6 +1494,224 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130100678</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Trunhatten SV, Skogskärr, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>466844</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6546459</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130100311</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Trunhatten SV, Trunhatten SV, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>466885</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6546699</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48284-2023 artfynd.xlsx
+++ b/artfynd/A 48284-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130100117</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130100329</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,6 +1038,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130100656</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1140,6 +1160,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130100671</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1257,6 +1282,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130101147</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1377,6 +1407,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115320239</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1494,6 +1529,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130099895</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1605,6 +1645,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130100678</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1712,8 +1757,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130100311</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>